--- a/Team-Data/2008-09/1-8-2008-09.xlsx
+++ b/Team-Data/2008-09/1-8-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>3</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -751,13 +818,13 @@
         <v>8</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
         <v>16</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
         <v>8</v>
@@ -769,13 +836,13 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>27</v>
@@ -793,13 +860,13 @@
         <v>5</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -808,13 +875,13 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>0.778</v>
+        <v>0.784</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J3" t="n">
-        <v>76.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="K3" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="L3" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.368</v>
+        <v>0.364</v>
       </c>
       <c r="O3" t="n">
         <v>21.5</v>
       </c>
       <c r="P3" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.772</v>
+        <v>0.767</v>
       </c>
       <c r="R3" t="n">
         <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V3" t="n">
         <v>16.2</v>
@@ -903,25 +970,25 @@
         <v>8.6</v>
       </c>
       <c r="X3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.9</v>
+        <v>100.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ3" t="n">
         <v>29</v>
@@ -948,31 +1015,31 @@
         <v>19</v>
       </c>
       <c r="AM3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN3" t="n">
         <v>14</v>
       </c>
       <c r="AO3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>30</v>
@@ -981,10 +1048,10 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
@@ -996,7 +1063,7 @@
         <v>9</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
@@ -1136,7 +1203,7 @@
         <v>19</v>
       </c>
       <c r="AO4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
@@ -1160,7 +1227,7 @@
         <v>24</v>
       </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX4" t="n">
         <v>21</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
         <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>0.412</v>
+        <v>0.429</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,79 +1292,79 @@
         <v>37</v>
       </c>
       <c r="J5" t="n">
-        <v>84.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L5" t="n">
         <v>6.3</v>
       </c>
       <c r="M5" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N5" t="n">
         <v>0.381</v>
       </c>
       <c r="O5" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="P5" t="n">
-        <v>23.6</v>
+        <v>24.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.801</v>
+        <v>0.799</v>
       </c>
       <c r="R5" t="n">
         <v>11.7</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="T5" t="n">
         <v>41.9</v>
       </c>
       <c r="U5" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="V5" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X5" t="n">
         <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>99.3</v>
+        <v>99.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG5" t="n">
         <v>18</v>
       </c>
-      <c r="AG5" t="n">
-        <v>20</v>
-      </c>
       <c r="AH5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="n">
         <v>10</v>
@@ -1306,58 +1373,58 @@
         <v>4</v>
       </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
       </c>
       <c r="AM5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
         <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
       </c>
       <c r="AU5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV5" t="n">
         <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ5" t="n">
         <v>23</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -1389,88 +1456,88 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
         <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.848</v>
+        <v>0.824</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J6" t="n">
-        <v>78.8</v>
+        <v>78.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.48</v>
+        <v>0.479</v>
       </c>
       <c r="L6" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M6" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.35</v>
+        <v>0.346</v>
       </c>
       <c r="O6" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R6" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S6" t="n">
         <v>30.9</v>
       </c>
       <c r="T6" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U6" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.4</v>
       </c>
       <c r="W6" t="n">
         <v>8.1</v>
       </c>
       <c r="X6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
+        <v>101.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
@@ -1482,28 +1549,28 @@
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
         <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN6" t="n">
         <v>20</v>
       </c>
       <c r="AO6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
         <v>15</v>
@@ -1521,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
         <v>7</v>
@@ -1530,13 +1597,13 @@
         <v>3</v>
       </c>
       <c r="AY6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
         <v>7</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>0.629</v>
+        <v>0.618</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
@@ -1589,28 +1656,28 @@
         <v>37.7</v>
       </c>
       <c r="J7" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>0.451</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.334</v>
+        <v>0.333</v>
       </c>
       <c r="O7" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P7" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.803</v>
+        <v>0.806</v>
       </c>
       <c r="R7" t="n">
         <v>11.8</v>
@@ -1622,37 +1689,37 @@
         <v>44.7</v>
       </c>
       <c r="U7" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V7" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="W7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="X7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
         <v>10</v>
@@ -1661,10 +1728,10 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ7" t="n">
         <v>6</v>
@@ -1673,13 +1740,13 @@
         <v>17</v>
       </c>
       <c r="AL7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
         <v>27</v>
@@ -1697,22 +1764,22 @@
         <v>1</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX7" t="n">
         <v>9</v>
       </c>
-      <c r="AV7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8</v>
-      </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
         <v>2</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1943,7 @@
         <v>24</v>
       </c>
       <c r="AS8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
         <v>21</v>
@@ -1885,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
@@ -1906,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>1</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF9" t="n">
         <v>7</v>
@@ -2028,13 +2095,13 @@
         <v>16</v>
       </c>
       <c r="AI9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
@@ -2043,7 +2110,7 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
         <v>26</v>
@@ -2058,31 +2125,31 @@
         <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT9" t="n">
         <v>19</v>
       </c>
       <c r="AU9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
         <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
         <v>5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB9" t="n">
         <v>26</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2268,7 @@
         <v>25</v>
       </c>
       <c r="AF10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG10" t="n">
         <v>26</v>
@@ -2243,7 +2310,7 @@
         <v>24</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
         <v>19</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -2389,13 +2456,13 @@
         <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI11" t="n">
         <v>29</v>
       </c>
       <c r="AJ11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK11" t="n">
         <v>27</v>
@@ -2422,13 +2489,13 @@
         <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV11" t="n">
         <v>13</v>
@@ -2440,7 +2507,7 @@
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -2583,22 +2650,22 @@
         <v>14</v>
       </c>
       <c r="AL12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM12" t="n">
         <v>9</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
         <v>22</v>
       </c>
       <c r="AP12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR12" t="n">
         <v>9</v>
@@ -2619,7 +2686,7 @@
         <v>16</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2628,7 +2695,7 @@
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" t="n">
         <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13" t="n">
-        <v>0.229</v>
+        <v>0.235</v>
       </c>
       <c r="H13" t="n">
         <v>48.9</v>
@@ -2681,40 +2748,40 @@
         <v>35.3</v>
       </c>
       <c r="J13" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.424</v>
+        <v>0.423</v>
       </c>
       <c r="L13" t="n">
         <v>5.1</v>
       </c>
       <c r="M13" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.315</v>
+        <v>0.311</v>
       </c>
       <c r="O13" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="P13" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S13" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="T13" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="U13" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="V13" t="n">
         <v>14.7</v>
@@ -2726,22 +2793,22 @@
         <v>6.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.7</v>
+        <v>-6.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2759,7 +2826,7 @@
         <v>26</v>
       </c>
       <c r="AJ13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK13" t="n">
         <v>30</v>
@@ -2774,22 +2841,22 @@
         <v>28</v>
       </c>
       <c r="AO13" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
         <v>27</v>
@@ -2804,10 +2871,10 @@
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
         <v>24</v>
@@ -2816,7 +2883,7 @@
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" t="n">
         <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.824</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J14" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K14" t="n">
         <v>0.471</v>
@@ -2872,31 +2939,31 @@
         <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.371</v>
+        <v>0.376</v>
       </c>
       <c r="O14" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="P14" t="n">
-        <v>28.2</v>
+        <v>27.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S14" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="T14" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="U14" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V14" t="n">
         <v>14</v>
@@ -2905,34 +2972,34 @@
         <v>9</v>
       </c>
       <c r="X14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y14" t="n">
         <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.7</v>
+        <v>107.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>27</v>
@@ -2947,31 +3014,31 @@
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM14" t="n">
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS14" t="n">
         <v>4</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
@@ -2983,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
         <v>9</v>
@@ -2998,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
@@ -3138,10 +3205,10 @@
         <v>26</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
@@ -3302,7 +3369,7 @@
         <v>17</v>
       </c>
       <c r="AI16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="n">
         <v>15</v>
@@ -3332,10 +3399,10 @@
         <v>19</v>
       </c>
       <c r="AS16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU16" t="n">
         <v>25</v>
@@ -3350,7 +3417,7 @@
         <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -3391,85 +3458,85 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" t="n">
         <v>17</v>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>0.472</v>
+        <v>0.459</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J17" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L17" t="n">
         <v>5.2</v>
       </c>
       <c r="M17" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.338</v>
+        <v>0.34</v>
       </c>
       <c r="O17" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="P17" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R17" t="n">
         <v>12.6</v>
       </c>
       <c r="S17" t="n">
-        <v>30.6</v>
+        <v>30.3</v>
       </c>
       <c r="T17" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="U17" t="n">
         <v>20.9</v>
       </c>
       <c r="V17" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W17" t="n">
         <v>7</v>
       </c>
       <c r="X17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
         <v>5</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3484,7 +3551,7 @@
         <v>12</v>
       </c>
       <c r="AI17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
         <v>10</v>
@@ -3511,13 +3578,13 @@
         <v>10</v>
       </c>
       <c r="AR17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU17" t="n">
         <v>12</v>
@@ -3526,7 +3593,7 @@
         <v>19</v>
       </c>
       <c r="AW17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3736,7 @@
         <v>14</v>
       </c>
       <c r="AJ18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
@@ -3693,10 +3760,10 @@
         <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
         <v>15</v>
@@ -3854,16 +3921,16 @@
         <v>13</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>6</v>
       </c>
       <c r="AM19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO19" t="n">
         <v>6</v>
@@ -3905,7 +3972,7 @@
         <v>12</v>
       </c>
       <c r="BB19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC19" t="n">
         <v>18</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4085,7 @@
         <v>29</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
@@ -4069,13 +4136,13 @@
         <v>24</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>8</v>
       </c>
       <c r="AX20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY20" t="n">
         <v>3</v>
@@ -4090,7 +4157,7 @@
         <v>22</v>
       </c>
       <c r="BC20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -4119,19 +4186,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E21" t="n">
         <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G21" t="n">
-        <v>0.382</v>
+        <v>0.394</v>
       </c>
       <c r="H21" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I21" t="n">
         <v>37.7</v>
@@ -4140,40 +4207,40 @@
         <v>86.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L21" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="M21" t="n">
         <v>29.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O21" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P21" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="Q21" t="n">
         <v>0.801</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
         <v>31.6</v>
       </c>
       <c r="T21" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U21" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="V21" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W21" t="n">
         <v>7.5</v>
@@ -4182,28 +4249,28 @@
         <v>2.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB21" t="n">
-        <v>103.6</v>
+        <v>103.9</v>
       </c>
       <c r="AC21" t="n">
         <v>-3.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
       </c>
       <c r="AF21" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AG21" t="n">
         <v>21</v>
@@ -4212,7 +4279,7 @@
         <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
@@ -4227,16 +4294,16 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4251,10 +4318,10 @@
         <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4266,7 +4333,7 @@
         <v>7</v>
       </c>
       <c r="BA21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB21" t="n">
         <v>4</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4418,25 +4485,25 @@
         <v>16</v>
       </c>
       <c r="AQ22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR22" t="n">
         <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT22" t="n">
         <v>16</v>
       </c>
       <c r="AU22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX22" t="n">
         <v>20</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -4561,16 +4628,16 @@
         <v>7.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
         <v>3</v>
       </c>
       <c r="AG23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH23" t="n">
         <v>25</v>
@@ -4579,10 +4646,10 @@
         <v>24</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4618,7 +4685,7 @@
         <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
         <v>5</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4816,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG24" t="n">
         <v>18</v>
@@ -4758,7 +4825,7 @@
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ24" t="n">
         <v>14</v>
@@ -4788,10 +4855,10 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
         <v>18</v>
@@ -4803,13 +4870,13 @@
         <v>9</v>
       </c>
       <c r="AX24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY24" t="n">
         <v>20</v>
       </c>
       <c r="AZ24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA24" t="n">
         <v>19</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -4988,10 +5055,10 @@
         <v>19</v>
       </c>
       <c r="AY25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -5029,106 +5096,106 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E26" t="n">
         <v>21</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>0.618</v>
+        <v>0.6</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="J26" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.456</v>
       </c>
       <c r="L26" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M26" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.386</v>
+        <v>0.387</v>
       </c>
       <c r="O26" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="P26" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.771</v>
+        <v>0.768</v>
       </c>
       <c r="R26" t="n">
         <v>12.9</v>
       </c>
       <c r="S26" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="T26" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U26" t="n">
         <v>20.6</v>
       </c>
       <c r="V26" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="W26" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X26" t="n">
         <v>5.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.2</v>
+        <v>97.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG26" t="n">
         <v>11</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AJ26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
@@ -5140,7 +5207,7 @@
         <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP26" t="n">
         <v>21</v>
@@ -5155,25 +5222,25 @@
         <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX26" t="n">
         <v>15</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
         <v>18</v>
@@ -5182,7 +5249,7 @@
         <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-9.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
@@ -5325,7 +5392,7 @@
         <v>17</v>
       </c>
       <c r="AP27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ27" t="n">
         <v>8</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -5393,46 +5460,46 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="H28" t="n">
         <v>48.9</v>
       </c>
       <c r="I28" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="J28" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="K28" t="n">
-        <v>0.467</v>
+        <v>0.466</v>
       </c>
       <c r="L28" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.406</v>
+        <v>0.407</v>
       </c>
       <c r="O28" t="n">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="P28" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R28" t="n">
         <v>8.300000000000001</v>
@@ -5444,34 +5511,34 @@
         <v>40</v>
       </c>
       <c r="U28" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V28" t="n">
         <v>12.2</v>
       </c>
       <c r="W28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="X28" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5489,7 +5556,7 @@
         <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
@@ -5498,7 +5565,7 @@
         <v>3</v>
       </c>
       <c r="AM28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5522,7 +5589,7 @@
         <v>25</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
@@ -5531,10 +5598,10 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5543,10 +5610,10 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>-2.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>18</v>
       </c>
       <c r="AF29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG29" t="n">
         <v>20</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>19</v>
       </c>
       <c r="AH29" t="n">
         <v>18</v>
@@ -5671,10 +5738,10 @@
         <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
         <v>16</v>
@@ -5704,7 +5771,7 @@
         <v>27</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
         <v>10</v>
@@ -5725,7 +5792,7 @@
         <v>20</v>
       </c>
       <c r="BB29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BC29" t="n">
         <v>20</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF30" t="n">
         <v>13</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>5</v>
@@ -5874,16 +5941,16 @@
         <v>5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS30" t="n">
         <v>20</v>
       </c>
       <c r="AT30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
@@ -5892,7 +5959,7 @@
         <v>27</v>
       </c>
       <c r="AW30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX30" t="n">
         <v>17</v>
@@ -5910,7 +5977,7 @@
         <v>8</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
@@ -6017,19 +6084,19 @@
         <v>-6.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI31" t="n">
         <v>19</v>
@@ -6053,7 +6120,7 @@
         <v>29</v>
       </c>
       <c r="AP31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
@@ -6077,22 +6144,22 @@
         <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY31" t="n">
         <v>18</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB31" t="n">
         <v>28</v>
       </c>
       <c r="BC31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-8-2008-09</t>
+          <t>2009-01-08</t>
         </is>
       </c>
     </row>
